--- a/Data/EXCEL/Transfer/salemon/202208/8021-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8021-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE331FE4-63B1-4C81-8939-419E3AD27B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{358A5DF4-27ED-4110-B12C-63A9D0B2AEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8021-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,20 +1227,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q252"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="5" width="10.125" customWidth="1"/>
-    <col min="6" max="7" width="11.125" customWidth="1"/>
-    <col min="8" max="8" width="10.125" customWidth="1"/>
-    <col min="9" max="9" width="9.5" customWidth="1"/>
-    <col min="10" max="13" width="10.125" customWidth="1"/>
-    <col min="14" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="10.125" customWidth="1"/>
-    <col min="17" max="17" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="16.75" customWidth="1"/>
+    <col min="2" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="7" width="15.375" customWidth="1"/>
+    <col min="8" max="8" width="14.125" customWidth="1"/>
+    <col min="9" max="9" width="13.375" customWidth="1"/>
+    <col min="10" max="13" width="14.125" customWidth="1"/>
+    <col min="14" max="15" width="13.375" customWidth="1"/>
+    <col min="16" max="16" width="14.125" customWidth="1"/>
+    <col min="17" max="17" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1259,7 +1267,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1298,7 +1306,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1341,7 +1349,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1380,7 +1388,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1433,7 +1441,7 @@
         <v>-0.96</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1486,7 +1494,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1539,7 +1547,7 @@
         <v>5.65</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1592,7 +1600,7 @@
         <v>9.94</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1645,7 +1653,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1698,7 +1706,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1751,7 +1759,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1804,7 +1812,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1857,7 +1865,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1910,7 +1918,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1963,7 +1971,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2016,7 +2024,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2069,7 +2077,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2122,7 +2130,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2175,7 +2183,7 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2228,7 +2236,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2281,7 +2289,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2334,7 +2342,7 @@
         <v>30.4</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2387,7 +2395,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2440,7 +2448,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2493,7 +2501,7 @@
         <v>-1.0900000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2546,7 +2554,7 @@
         <v>-0.92</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2599,7 +2607,7 @@
         <v>-1.92</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2652,7 +2660,7 @@
         <v>-3.1</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2705,7 +2713,7 @@
         <v>-4.21</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2758,7 +2766,7 @@
         <v>-5.58</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2811,7 +2819,7 @@
         <v>-6.34</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2864,7 +2872,7 @@
         <v>-7.68</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2917,7 +2925,7 @@
         <v>-8.09</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2970,7 +2978,7 @@
         <v>-8.75</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3023,7 +3031,7 @@
         <v>-14.4</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3076,7 +3084,7 @@
         <v>-20.6</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3129,7 +3137,7 @@
         <v>-8.41</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3182,7 +3190,7 @@
         <v>-9.4</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3235,7 +3243,7 @@
         <v>-9.41</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3288,7 +3296,7 @@
         <v>-9.4</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3341,7 +3349,7 @@
         <v>-8.94</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3394,7 +3402,7 @@
         <v>-7.98</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3447,7 +3455,7 @@
         <v>-9.1300000000000008</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3500,7 +3508,7 @@
         <v>-10.199999999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3553,7 +3561,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3606,7 +3614,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3659,7 +3667,7 @@
         <v>-17.899999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3712,7 +3720,7 @@
         <v>-8.02</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3765,7 +3773,7 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3818,7 +3826,7 @@
         <v>-0.28999999999999998</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3871,7 +3879,7 @@
         <v>-0.23</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3924,7 +3932,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3977,7 +3985,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4030,7 +4038,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4083,7 +4091,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4136,7 +4144,7 @@
         <v>2.2200000000000002</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4189,7 +4197,7 @@
         <v>-0.15</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4242,7 +4250,7 @@
         <v>-1.31</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4295,7 +4303,7 @@
         <v>-0.86</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4348,7 +4356,7 @@
         <v>-1.99</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4401,7 +4409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4454,7 +4462,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4507,7 +4515,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4560,7 +4568,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4613,7 +4621,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4666,7 +4674,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4719,7 +4727,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4772,7 +4780,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4825,7 +4833,7 @@
         <v>9.14</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4878,7 +4886,7 @@
         <v>9.7100000000000009</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4931,7 +4939,7 @@
         <v>9.27</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4984,7 +4992,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5037,7 +5045,7 @@
         <v>-6.35</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5090,7 +5098,7 @@
         <v>-7.62</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5143,7 +5151,7 @@
         <v>-8.76</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5196,7 +5204,7 @@
         <v>-9.48</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5249,7 +5257,7 @@
         <v>-9.94</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5302,7 +5310,7 @@
         <v>-9.39</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5355,7 +5363,7 @@
         <v>-9.18</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5408,7 +5416,7 @@
         <v>-11.2</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5461,7 +5469,7 @@
         <v>-10.3</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5514,7 +5522,7 @@
         <v>-9.5500000000000007</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5567,7 +5575,7 @@
         <v>-9.2100000000000009</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5620,7 +5628,7 @@
         <v>-8.0299999999999994</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5673,7 +5681,7 @@
         <v>8.26</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5726,7 +5734,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5779,7 +5787,7 @@
         <v>9.42</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5832,7 +5840,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5885,7 +5893,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5938,7 +5946,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5991,7 +5999,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6044,7 +6052,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6097,7 +6105,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6150,7 +6158,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6203,7 +6211,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6256,7 +6264,7 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41974</v>
       </c>
@@ -6309,7 +6317,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41944</v>
       </c>
@@ -6362,7 +6370,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41913</v>
       </c>
@@ -6415,7 +6423,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41883</v>
       </c>
@@ -6468,7 +6476,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41852</v>
       </c>
@@ -6521,7 +6529,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41821</v>
       </c>
@@ -6574,7 +6582,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41791</v>
       </c>
@@ -6627,7 +6635,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41760</v>
       </c>
@@ -6680,7 +6688,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41730</v>
       </c>
@@ -6733,7 +6741,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41699</v>
       </c>
@@ -6786,7 +6794,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41671</v>
       </c>
@@ -6839,7 +6847,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41640</v>
       </c>
@@ -6892,7 +6900,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41609</v>
       </c>
@@ -6945,7 +6953,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41579</v>
       </c>
@@ -6998,7 +7006,7 @@
         <v>7.79</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41548</v>
       </c>
@@ -7051,7 +7059,7 @@
         <v>9.3800000000000008</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41518</v>
       </c>
@@ -7104,7 +7112,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41487</v>
       </c>
@@ -7157,7 +7165,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41456</v>
       </c>
@@ -7210,7 +7218,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41426</v>
       </c>
@@ -7263,7 +7271,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41395</v>
       </c>
@@ -7316,7 +7324,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41365</v>
       </c>
@@ -7369,7 +7377,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41334</v>
       </c>
@@ -7422,7 +7430,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41306</v>
       </c>
@@ -7475,7 +7483,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41275</v>
       </c>
@@ -7528,7 +7536,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41244</v>
       </c>
@@ -7581,7 +7589,7 @@
         <v>6.15</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41214</v>
       </c>
@@ -7634,7 +7642,7 @@
         <v>5.27</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41183</v>
       </c>
@@ -7687,7 +7695,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41153</v>
       </c>
@@ -7740,7 +7748,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>41122</v>
       </c>
@@ -7793,7 +7801,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>41091</v>
       </c>
@@ -7846,7 +7854,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>41061</v>
       </c>
@@ -7899,7 +7907,7 @@
         <v>-0.48</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>41030</v>
       </c>
@@ -7952,7 +7960,7 @@
         <v>-0.47</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>41000</v>
       </c>
@@ -8005,7 +8013,7 @@
         <v>-3.63</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>40969</v>
       </c>
@@ -8058,7 +8066,7 @@
         <v>-8.99</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="5" customFormat="1">
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>40940</v>
       </c>
@@ -8111,7 +8119,7 @@
         <v>-12.6</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="5" customFormat="1">
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>40909</v>
       </c>
@@ -8164,7 +8172,7 @@
         <v>-21.1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" s="5" customFormat="1">
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>40878</v>
       </c>
@@ -8217,7 +8225,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="134" spans="1:17" s="5" customFormat="1">
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>40848</v>
       </c>
@@ -8270,7 +8278,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="135" spans="1:17" s="5" customFormat="1">
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>40817</v>
       </c>
@@ -8323,7 +8331,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="136" spans="1:17" s="5" customFormat="1">
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>40787</v>
       </c>
@@ -8376,7 +8384,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="137" spans="1:17" s="5" customFormat="1">
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>40756</v>
       </c>
@@ -8429,7 +8437,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="138" spans="1:17" s="5" customFormat="1">
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>40725</v>
       </c>
@@ -8482,7 +8490,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="139" spans="1:17" s="5" customFormat="1">
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>40695</v>
       </c>
@@ -8535,7 +8543,7 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="140" spans="1:17" s="5" customFormat="1">
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>40664</v>
       </c>
@@ -8588,7 +8596,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="141" spans="1:17" s="5" customFormat="1">
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>40634</v>
       </c>
@@ -8641,7 +8649,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="142" spans="1:17" s="5" customFormat="1">
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>40603</v>
       </c>
@@ -8694,7 +8702,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="143" spans="1:17" s="5" customFormat="1">
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>40575</v>
       </c>
@@ -8747,7 +8755,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:17" s="5" customFormat="1">
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>40544</v>
       </c>
@@ -8800,7 +8808,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="145" spans="1:17" s="5" customFormat="1">
+    <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>40513</v>
       </c>
@@ -8853,7 +8861,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="146" spans="1:17" s="5" customFormat="1">
+    <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>40483</v>
       </c>
@@ -8906,7 +8914,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="147" spans="1:17" s="5" customFormat="1">
+    <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>40452</v>
       </c>
@@ -8959,7 +8967,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="148" spans="1:17" s="5" customFormat="1">
+    <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>40422</v>
       </c>
@@ -9012,7 +9020,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="149" spans="1:17" s="5" customFormat="1">
+    <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>40391</v>
       </c>
@@ -9065,7 +9073,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="150" spans="1:17" s="5" customFormat="1">
+    <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>40360</v>
       </c>
@@ -9118,7 +9126,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="151" spans="1:17" s="5" customFormat="1">
+    <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>40330</v>
       </c>
@@ -9171,7 +9179,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="152" spans="1:17" s="5" customFormat="1">
+    <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>40299</v>
       </c>
@@ -9224,7 +9232,7 @@
         <v>34.6</v>
       </c>
     </row>
-    <row r="153" spans="1:17" s="5" customFormat="1">
+    <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>40269</v>
       </c>
@@ -9277,7 +9285,7 @@
         <v>36.700000000000003</v>
       </c>
     </row>
-    <row r="154" spans="1:17" s="5" customFormat="1">
+    <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>40238</v>
       </c>
@@ -9330,7 +9338,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="155" spans="1:17" s="5" customFormat="1">
+    <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>40210</v>
       </c>
@@ -9383,7 +9391,7 @@
         <v>69.8</v>
       </c>
     </row>
-    <row r="156" spans="1:17" s="5" customFormat="1">
+    <row r="156" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>40179</v>
       </c>
@@ -9436,7 +9444,7 @@
         <v>89.1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" s="5" customFormat="1">
+    <row r="157" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>40148</v>
       </c>
@@ -9489,7 +9497,7 @@
         <v>-13.1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" s="5" customFormat="1">
+    <row r="158" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>40118</v>
       </c>
@@ -9542,7 +9550,7 @@
         <v>-17.2</v>
       </c>
     </row>
-    <row r="159" spans="1:17" s="5" customFormat="1">
+    <row r="159" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>40087</v>
       </c>
@@ -9595,7 +9603,7 @@
         <v>-19.5</v>
       </c>
     </row>
-    <row r="160" spans="1:17" s="5" customFormat="1">
+    <row r="160" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>40057</v>
       </c>
@@ -9648,7 +9656,7 @@
         <v>-19.899999999999999</v>
       </c>
     </row>
-    <row r="161" spans="1:17" s="5" customFormat="1">
+    <row r="161" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
         <v>40026</v>
       </c>
@@ -9701,7 +9709,7 @@
         <v>-18.7</v>
       </c>
     </row>
-    <row r="162" spans="1:17" s="5" customFormat="1">
+    <row r="162" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
         <v>39995</v>
       </c>
@@ -9754,7 +9762,7 @@
         <v>-17.8</v>
       </c>
     </row>
-    <row r="163" spans="1:17" s="5" customFormat="1">
+    <row r="163" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>39965</v>
       </c>
@@ -9807,7 +9815,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="164" spans="1:17" s="5" customFormat="1">
+    <row r="164" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
         <v>39934</v>
       </c>
@@ -9860,7 +9868,7 @@
         <v>-18.5</v>
       </c>
     </row>
-    <row r="165" spans="1:17" s="5" customFormat="1">
+    <row r="165" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
         <v>39904</v>
       </c>
@@ -9913,7 +9921,7 @@
         <v>-19.5</v>
       </c>
     </row>
-    <row r="166" spans="1:17" s="5" customFormat="1">
+    <row r="166" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
         <v>39873</v>
       </c>
@@ -9966,7 +9974,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="167" spans="1:17" s="5" customFormat="1">
+    <row r="167" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>39845</v>
       </c>
@@ -10019,7 +10027,7 @@
         <v>-36.1</v>
       </c>
     </row>
-    <row r="168" spans="1:17" s="5" customFormat="1">
+    <row r="168" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
         <v>39814</v>
       </c>
@@ -10072,7 +10080,7 @@
         <v>-51.5</v>
       </c>
     </row>
-    <row r="169" spans="1:17" s="5" customFormat="1">
+    <row r="169" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
         <v>39783</v>
       </c>
@@ -10125,7 +10133,7 @@
         <v>-7.8</v>
       </c>
     </row>
-    <row r="170" spans="1:17" s="5" customFormat="1">
+    <row r="170" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>39753</v>
       </c>
@@ -10178,7 +10186,7 @@
         <v>-2.85</v>
       </c>
     </row>
-    <row r="171" spans="1:17" s="5" customFormat="1">
+    <row r="171" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>39722</v>
       </c>
@@ -10231,7 +10239,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="172" spans="1:17" s="5" customFormat="1">
+    <row r="172" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>39692</v>
       </c>
@@ -10284,7 +10292,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="173" spans="1:17" s="5" customFormat="1">
+    <row r="173" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>39661</v>
       </c>
@@ -10337,7 +10345,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="174" spans="1:17" s="5" customFormat="1">
+    <row r="174" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
         <v>39630</v>
       </c>
@@ -10390,7 +10398,7 @@
         <v>-0.82</v>
       </c>
     </row>
-    <row r="175" spans="1:17" s="5" customFormat="1">
+    <row r="175" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
         <v>39600</v>
       </c>
@@ -10443,7 +10451,7 @@
         <v>-1.08</v>
       </c>
     </row>
-    <row r="176" spans="1:17" s="5" customFormat="1">
+    <row r="176" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>39569</v>
       </c>
@@ -10496,7 +10504,7 @@
         <v>-2.23</v>
       </c>
     </row>
-    <row r="177" spans="1:17" s="5" customFormat="1">
+    <row r="177" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>39539</v>
       </c>
@@ -10549,7 +10557,7 @@
         <v>-5.52</v>
       </c>
     </row>
-    <row r="178" spans="1:17" s="5" customFormat="1">
+    <row r="178" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>39508</v>
       </c>
@@ -10602,7 +10610,7 @@
         <v>-4.84</v>
       </c>
     </row>
-    <row r="179" spans="1:17" s="5" customFormat="1">
+    <row r="179" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>39479</v>
       </c>
@@ -10655,7 +10663,7 @@
         <v>-6.46</v>
       </c>
     </row>
-    <row r="180" spans="1:17" s="5" customFormat="1">
+    <row r="180" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>39448</v>
       </c>
@@ -10708,7 +10716,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="181" spans="1:17" s="5" customFormat="1">
+    <row r="181" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>39417</v>
       </c>
@@ -10761,7 +10769,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="182" spans="1:17" s="5" customFormat="1">
+    <row r="182" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>39387</v>
       </c>
@@ -10814,7 +10822,7 @@
         <v>36.299999999999997</v>
       </c>
     </row>
-    <row r="183" spans="1:17" s="5" customFormat="1">
+    <row r="183" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>39356</v>
       </c>
@@ -10867,7 +10875,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="184" spans="1:17" s="5" customFormat="1">
+    <row r="184" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>39326</v>
       </c>
@@ -10920,7 +10928,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="185" spans="1:17" s="5" customFormat="1">
+    <row r="185" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>39295</v>
       </c>
@@ -10973,7 +10981,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="186" spans="1:17" s="5" customFormat="1">
+    <row r="186" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
         <v>39264</v>
       </c>
@@ -11026,7 +11034,7 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="187" spans="1:17" s="5" customFormat="1">
+    <row r="187" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
         <v>39234</v>
       </c>
@@ -11079,7 +11087,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="188" spans="1:17" s="5" customFormat="1">
+    <row r="188" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
         <v>39203</v>
       </c>
@@ -11132,7 +11140,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="189" spans="1:17" s="5" customFormat="1">
+    <row r="189" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
         <v>39173</v>
       </c>
@@ -11185,7 +11193,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" spans="1:17" s="5" customFormat="1">
+    <row r="190" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
         <v>39142</v>
       </c>
@@ -11238,7 +11246,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="191" spans="1:17" s="5" customFormat="1">
+    <row r="191" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
         <v>39114</v>
       </c>
@@ -11291,7 +11299,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="192" spans="1:17" s="5" customFormat="1">
+    <row r="192" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
         <v>39083</v>
       </c>
@@ -11344,7 +11352,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="193" spans="1:17" s="5" customFormat="1">
+    <row r="193" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
         <v>39052</v>
       </c>
@@ -11397,7 +11405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:17" s="5" customFormat="1">
+    <row r="194" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A194" s="6">
         <v>39022</v>
       </c>
@@ -11450,7 +11458,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:17" s="5" customFormat="1">
+    <row r="195" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A195" s="6">
         <v>38991</v>
       </c>
@@ -11503,7 +11511,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="196" spans="1:17" s="5" customFormat="1">
+    <row r="196" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A196" s="6">
         <v>38961</v>
       </c>
@@ -11556,7 +11564,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:17" s="5" customFormat="1">
+    <row r="197" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A197" s="6">
         <v>38930</v>
       </c>
@@ -11609,7 +11617,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:17" s="5" customFormat="1">
+    <row r="198" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
         <v>38899</v>
       </c>
@@ -11662,7 +11670,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:17" s="5" customFormat="1">
+    <row r="199" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A199" s="6">
         <v>38869</v>
       </c>
@@ -11715,7 +11723,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:17" s="5" customFormat="1">
+    <row r="200" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <v>38838</v>
       </c>
@@ -11768,7 +11776,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:17" s="5" customFormat="1">
+    <row r="201" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A201" s="6">
         <v>38808</v>
       </c>
@@ -11821,7 +11829,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:17" s="5" customFormat="1">
+    <row r="202" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A202" s="6">
         <v>38777</v>
       </c>
@@ -11874,7 +11882,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:17" s="5" customFormat="1">
+    <row r="203" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
         <v>38749</v>
       </c>
@@ -11927,7 +11935,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="204" spans="1:17" s="5" customFormat="1">
+    <row r="204" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A204" s="6">
         <v>38718</v>
       </c>
@@ -11980,7 +11988,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:17" s="5" customFormat="1">
+    <row r="205" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
         <v>38687</v>
       </c>
@@ -12033,7 +12041,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:17" s="5" customFormat="1">
+    <row r="206" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A206" s="6">
         <v>38657</v>
       </c>
@@ -12086,7 +12094,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:17" s="5" customFormat="1">
+    <row r="207" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A207" s="6">
         <v>38626</v>
       </c>
@@ -12139,7 +12147,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:17" s="5" customFormat="1">
+    <row r="208" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A208" s="6">
         <v>38596</v>
       </c>
@@ -12192,7 +12200,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:17" s="5" customFormat="1">
+    <row r="209" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
         <v>38565</v>
       </c>
@@ -12245,7 +12253,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:17" s="5" customFormat="1">
+    <row r="210" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A210" s="6">
         <v>38534</v>
       </c>
@@ -12298,7 +12306,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:17" s="5" customFormat="1">
+    <row r="211" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A211" s="6">
         <v>38504</v>
       </c>
@@ -12351,7 +12359,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:17" s="5" customFormat="1">
+    <row r="212" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A212" s="6">
         <v>38473</v>
       </c>
@@ -12404,7 +12412,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:17" s="5" customFormat="1">
+    <row r="213" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
         <v>38443</v>
       </c>
@@ -12457,7 +12465,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:17" s="5" customFormat="1">
+    <row r="214" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A214" s="6">
         <v>38412</v>
       </c>
@@ -12510,7 +12518,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:17" s="5" customFormat="1">
+    <row r="215" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A215" s="6">
         <v>38384</v>
       </c>
@@ -12563,7 +12571,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:17" s="5" customFormat="1">
+    <row r="216" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>38353</v>
       </c>
@@ -12616,7 +12624,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:17" s="5" customFormat="1">
+    <row r="217" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A217" s="6">
         <v>38322</v>
       </c>
@@ -12669,7 +12677,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:17" s="5" customFormat="1">
+    <row r="218" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A218" s="6">
         <v>38292</v>
       </c>
@@ -12722,7 +12730,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="219" spans="1:17" s="5" customFormat="1">
+    <row r="219" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A219" s="6">
         <v>38261</v>
       </c>
@@ -12775,7 +12783,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:17" s="5" customFormat="1">
+    <row r="220" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>38231</v>
       </c>
@@ -12828,7 +12836,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="221" spans="1:17" s="5" customFormat="1">
+    <row r="221" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
         <v>38200</v>
       </c>
@@ -12881,7 +12889,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:17" s="5" customFormat="1">
+    <row r="222" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>38169</v>
       </c>
@@ -12934,7 +12942,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" spans="1:17" s="5" customFormat="1">
+    <row r="223" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A223" s="6">
         <v>38139</v>
       </c>
@@ -12987,7 +12995,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:17" s="5" customFormat="1">
+    <row r="224" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>38108</v>
       </c>
@@ -13040,7 +13048,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" spans="1:17" s="5" customFormat="1">
+    <row r="225" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A225" s="6">
         <v>38078</v>
       </c>
@@ -13093,7 +13101,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:17" s="5" customFormat="1">
+    <row r="226" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>38047</v>
       </c>
@@ -13146,7 +13154,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" spans="1:17" s="5" customFormat="1">
+    <row r="227" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A227" s="6">
         <v>38018</v>
       </c>
@@ -13199,7 +13207,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:17" s="5" customFormat="1">
+    <row r="228" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>37987</v>
       </c>
@@ -13252,7 +13260,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" spans="1:17" s="5" customFormat="1">
+    <row r="229" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A229" s="6">
         <v>37956</v>
       </c>
@@ -13305,7 +13313,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" spans="1:17" s="5" customFormat="1">
+    <row r="230" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>37926</v>
       </c>
@@ -13358,7 +13366,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:17" s="5" customFormat="1">
+    <row r="231" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A231" s="6">
         <v>37895</v>
       </c>
@@ -13411,7 +13419,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" spans="1:17" s="5" customFormat="1">
+    <row r="232" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>37865</v>
       </c>
@@ -13464,7 +13472,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="233" spans="1:17" s="5" customFormat="1">
+    <row r="233" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A233" s="6">
         <v>37834</v>
       </c>
@@ -13517,7 +13525,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:17" s="5" customFormat="1">
+    <row r="234" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>37803</v>
       </c>
@@ -13570,7 +13578,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" spans="1:17" s="5" customFormat="1">
+    <row r="235" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
         <v>37773</v>
       </c>
@@ -13623,7 +13631,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:17" s="5" customFormat="1">
+    <row r="236" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A236" s="6">
         <v>37742</v>
       </c>
@@ -13676,7 +13684,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:17" s="5" customFormat="1">
+    <row r="237" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A237" s="6">
         <v>37712</v>
       </c>
@@ -13729,7 +13737,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="238" spans="1:17" s="5" customFormat="1">
+    <row r="238" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A238" s="6">
         <v>37681</v>
       </c>
@@ -13782,7 +13790,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="239" spans="1:17" s="5" customFormat="1">
+    <row r="239" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
         <v>37653</v>
       </c>
@@ -13835,7 +13843,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:17" s="5" customFormat="1">
+    <row r="240" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A240" s="6">
         <v>37622</v>
       </c>
@@ -13888,7 +13896,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="241" spans="1:17" s="5" customFormat="1">
+    <row r="241" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A241" s="6">
         <v>37591</v>
       </c>
@@ -13941,7 +13949,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="242" spans="1:17" s="5" customFormat="1">
+    <row r="242" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A242" s="6">
         <v>37561</v>
       </c>
@@ -13994,7 +14002,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="243" spans="1:17" s="5" customFormat="1">
+    <row r="243" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A243" s="6">
         <v>37530</v>
       </c>
@@ -14047,7 +14055,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="244" spans="1:17" s="5" customFormat="1">
+    <row r="244" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A244" s="6">
         <v>37500</v>
       </c>
@@ -14100,7 +14108,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="245" spans="1:17" s="5" customFormat="1">
+    <row r="245" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A245" s="6">
         <v>37469</v>
       </c>
@@ -14153,7 +14161,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="246" spans="1:17" s="5" customFormat="1">
+    <row r="246" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A246" s="6">
         <v>37438</v>
       </c>
@@ -14206,7 +14214,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="247" spans="1:17" s="5" customFormat="1">
+    <row r="247" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A247" s="6">
         <v>37408</v>
       </c>
@@ -14259,7 +14267,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="248" spans="1:17" s="5" customFormat="1">
+    <row r="248" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A248" s="6">
         <v>37377</v>
       </c>
@@ -14312,7 +14320,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="249" spans="1:17" s="5" customFormat="1">
+    <row r="249" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A249" s="6">
         <v>37347</v>
       </c>
@@ -14365,7 +14373,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" spans="1:17" s="5" customFormat="1">
+    <row r="250" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A250" s="6">
         <v>37316</v>
       </c>
@@ -14418,7 +14426,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="251" spans="1:17" s="5" customFormat="1">
+    <row r="251" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A251" s="6">
         <v>37288</v>
       </c>
@@ -14471,7 +14479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="252" spans="1:17" s="5" customFormat="1">
+    <row r="252" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A252" s="6">
         <v>37257</v>
       </c>
@@ -14539,7 +14547,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>